--- a/AJG2024.xlsx
+++ b/AJG2024.xlsx
@@ -1940,7 +1940,11 @@
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2293,7 +2297,11 @@
         <v>2</v>
       </c>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4184,7 +4192,11 @@
         <v>1</v>
       </c>
       <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -4714,7 +4726,11 @@
         <v>2</v>
       </c>
       <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -4747,7 +4763,11 @@
       <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -4905,7 +4925,11 @@
       <c r="J107" t="n">
         <v>2</v>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -4989,7 +5013,11 @@
       <c r="J109" t="n">
         <v>2</v>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -8379,7 +8407,11 @@
       <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr"/>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -8686,7 +8718,11 @@
       <c r="J192" t="n">
         <v>3</v>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -9570,7 +9606,11 @@
       <c r="J212" t="n">
         <v>2</v>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -9767,7 +9807,11 @@
         <v>2</v>
       </c>
       <c r="J217" t="inlineStr"/>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -10111,7 +10155,11 @@
         <v>2</v>
       </c>
       <c r="J225" t="inlineStr"/>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -11503,7 +11551,11 @@
         <v>2</v>
       </c>
       <c r="J257" t="inlineStr"/>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -11937,7 +11989,11 @@
       <c r="J267" t="n">
         <v>3</v>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -12062,7 +12118,11 @@
       </c>
       <c r="I270" t="inlineStr"/>
       <c r="J270" t="inlineStr"/>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -12494,7 +12554,11 @@
         <v>2</v>
       </c>
       <c r="J280" t="inlineStr"/>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -13020,7 +13084,11 @@
         <v>2</v>
       </c>
       <c r="J292" t="inlineStr"/>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -13186,7 +13254,11 @@
       <c r="J296" t="n">
         <v>2</v>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -13315,7 +13387,11 @@
         <v>2</v>
       </c>
       <c r="J299" t="inlineStr"/>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -13616,7 +13692,11 @@
         <v>2</v>
       </c>
       <c r="J306" t="inlineStr"/>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -14087,7 +14167,11 @@
       <c r="J317" t="n">
         <v>2</v>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -14523,7 +14607,11 @@
         <v>2</v>
       </c>
       <c r="J327" t="inlineStr"/>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -14564,7 +14652,11 @@
       <c r="J328" t="n">
         <v>2</v>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -15126,7 +15218,11 @@
         <v>1</v>
       </c>
       <c r="J342" t="inlineStr"/>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -15249,7 +15345,11 @@
       </c>
       <c r="I345" t="inlineStr"/>
       <c r="J345" t="inlineStr"/>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -15657,7 +15757,11 @@
         <v>1</v>
       </c>
       <c r="J355" t="inlineStr"/>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -15811,7 +15915,11 @@
         <v>1</v>
       </c>
       <c r="J359" t="inlineStr"/>
-      <c r="K359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -16332,7 +16440,11 @@
         <v>1</v>
       </c>
       <c r="J372" t="inlineStr"/>
-      <c r="K372" t="inlineStr"/>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -16453,7 +16565,11 @@
       <c r="J375" t="n">
         <v>1</v>
       </c>
-      <c r="K375" t="inlineStr"/>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -16572,7 +16688,11 @@
       </c>
       <c r="I378" t="inlineStr"/>
       <c r="J378" t="inlineStr"/>
-      <c r="K378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -17325,7 +17445,11 @@
         <v>1</v>
       </c>
       <c r="J397" t="inlineStr"/>
-      <c r="K397" t="inlineStr"/>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -17401,7 +17525,11 @@
       <c r="H399" t="inlineStr"/>
       <c r="I399" t="inlineStr"/>
       <c r="J399" t="inlineStr"/>
-      <c r="K399" t="inlineStr"/>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -17874,7 +18002,11 @@
         <v>1</v>
       </c>
       <c r="J410" t="inlineStr"/>
-      <c r="K410" t="inlineStr"/>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -18426,7 +18558,11 @@
       <c r="H424" t="inlineStr"/>
       <c r="I424" t="inlineStr"/>
       <c r="J424" t="inlineStr"/>
-      <c r="K424" t="inlineStr"/>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
@@ -18787,7 +18923,11 @@
       <c r="J433" t="n">
         <v>1</v>
       </c>
-      <c r="K433" t="inlineStr"/>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
@@ -19070,7 +19210,11 @@
       <c r="J440" t="n">
         <v>1</v>
       </c>
-      <c r="K440" t="inlineStr"/>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
@@ -19316,7 +19460,11 @@
         <v>1</v>
       </c>
       <c r="J446" t="inlineStr"/>
-      <c r="K446" t="inlineStr"/>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
@@ -19480,7 +19628,11 @@
       <c r="H450" t="inlineStr"/>
       <c r="I450" t="inlineStr"/>
       <c r="J450" t="inlineStr"/>
-      <c r="K450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
@@ -20157,7 +20309,11 @@
         <v>1</v>
       </c>
       <c r="J467" t="inlineStr"/>
-      <c r="K467" t="inlineStr"/>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
@@ -20958,7 +21114,11 @@
       </c>
       <c r="I486" t="inlineStr"/>
       <c r="J486" t="inlineStr"/>
-      <c r="K486" t="inlineStr"/>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
@@ -21323,7 +21483,11 @@
       </c>
       <c r="I495" t="inlineStr"/>
       <c r="J495" t="inlineStr"/>
-      <c r="K495" t="inlineStr"/>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
@@ -21910,7 +22074,11 @@
       <c r="J510" t="n">
         <v>1</v>
       </c>
-      <c r="K510" t="inlineStr"/>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="n">
@@ -25193,7 +25361,11 @@
       </c>
       <c r="I589" t="inlineStr"/>
       <c r="J589" t="inlineStr"/>
-      <c r="K589" t="inlineStr"/>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
     </row>
     <row r="590">
       <c r="A590" t="n">
@@ -28307,7 +28479,11 @@
       <c r="J663" t="n">
         <v>1</v>
       </c>
-      <c r="K663" t="inlineStr"/>
+      <c r="K663" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
     </row>
     <row r="664">
       <c r="A664" t="n">
@@ -29479,7 +29655,11 @@
         <v>2</v>
       </c>
       <c r="J691" t="inlineStr"/>
-      <c r="K691" t="inlineStr"/>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
     </row>
     <row r="692">
       <c r="A692" t="n">
@@ -29786,7 +29966,11 @@
       <c r="J698" t="n">
         <v>2</v>
       </c>
-      <c r="K698" t="inlineStr"/>
+      <c r="K698" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="699">
       <c r="A699" t="n">
@@ -34151,7 +34335,11 @@
       </c>
       <c r="I805" t="inlineStr"/>
       <c r="J805" t="inlineStr"/>
-      <c r="K805" t="inlineStr"/>
+      <c r="K805" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
     </row>
     <row r="806">
       <c r="A806" t="n">
@@ -35656,7 +35844,11 @@
       <c r="J840" t="n">
         <v>1</v>
       </c>
-      <c r="K840" t="inlineStr"/>
+      <c r="K840" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
     </row>
     <row r="841">
       <c r="A841" t="n">
@@ -36197,7 +36389,11 @@
       <c r="J853" t="n">
         <v>1</v>
       </c>
-      <c r="K853" t="inlineStr"/>
+      <c r="K853" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
     </row>
     <row r="854">
       <c r="A854" t="n">
@@ -36273,7 +36469,11 @@
       </c>
       <c r="I855" t="inlineStr"/>
       <c r="J855" t="inlineStr"/>
-      <c r="K855" t="inlineStr"/>
+      <c r="K855" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
     </row>
     <row r="856">
       <c r="A856" t="n">
@@ -37403,7 +37603,11 @@
         <v>1</v>
       </c>
       <c r="J881" t="inlineStr"/>
-      <c r="K881" t="inlineStr"/>
+      <c r="K881" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
     </row>
     <row r="882">
       <c r="A882" t="n">
@@ -39800,7 +40004,11 @@
       </c>
       <c r="I938" t="inlineStr"/>
       <c r="J938" t="inlineStr"/>
-      <c r="K938" t="inlineStr"/>
+      <c r="K938" t="inlineStr">
+        <is>
+          <t>&lt;0.1</t>
+        </is>
+      </c>
     </row>
     <row r="939">
       <c r="A939" t="n">
@@ -39999,7 +40207,11 @@
       </c>
       <c r="I943" t="inlineStr"/>
       <c r="J943" t="inlineStr"/>
-      <c r="K943" t="inlineStr"/>
+      <c r="K943" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
     </row>
     <row r="944">
       <c r="A944" t="n">
@@ -40801,7 +41013,11 @@
         <v>1</v>
       </c>
       <c r="J963" t="inlineStr"/>
-      <c r="K963" t="inlineStr"/>
+      <c r="K963" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
     </row>
     <row r="964">
       <c r="A964" t="n">
@@ -44058,7 +44274,11 @@
       <c r="H1042" t="inlineStr"/>
       <c r="I1042" t="inlineStr"/>
       <c r="J1042" t="inlineStr"/>
-      <c r="K1042" t="inlineStr"/>
+      <c r="K1042" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
     </row>
     <row r="1043">
       <c r="A1043" t="n">
@@ -44128,7 +44348,11 @@
       <c r="H1044" t="inlineStr"/>
       <c r="I1044" t="inlineStr"/>
       <c r="J1044" t="inlineStr"/>
-      <c r="K1044" t="inlineStr"/>
+      <c r="K1044" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
     </row>
     <row r="1045">
       <c r="A1045" t="n">
@@ -47590,7 +47814,11 @@
       <c r="H1124" t="inlineStr"/>
       <c r="I1124" t="inlineStr"/>
       <c r="J1124" t="inlineStr"/>
-      <c r="K1124" t="inlineStr"/>
+      <c r="K1124" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
     </row>
     <row r="1125">
       <c r="A1125" t="n">
@@ -49597,7 +49825,11 @@
       <c r="J1171" t="n">
         <v>1</v>
       </c>
-      <c r="K1171" t="inlineStr"/>
+      <c r="K1171" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
     </row>
     <row r="1172">
       <c r="A1172" t="n">
@@ -53334,7 +53566,11 @@
       <c r="J1260" t="n">
         <v>2</v>
       </c>
-      <c r="K1260" t="inlineStr"/>
+      <c r="K1260" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
     </row>
     <row r="1261">
       <c r="A1261" t="n">
@@ -53373,7 +53609,11 @@
         <v>2</v>
       </c>
       <c r="J1261" t="inlineStr"/>
-      <c r="K1261" t="inlineStr"/>
+      <c r="K1261" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
     </row>
     <row r="1262">
       <c r="A1262" t="n">
@@ -54529,7 +54769,11 @@
         <v>1</v>
       </c>
       <c r="J1289" t="inlineStr"/>
-      <c r="K1289" t="inlineStr"/>
+      <c r="K1289" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
     </row>
     <row r="1290">
       <c r="A1290" t="n">
@@ -55952,7 +56196,11 @@
       <c r="H1322" t="inlineStr"/>
       <c r="I1322" t="inlineStr"/>
       <c r="J1322" t="inlineStr"/>
-      <c r="K1322" t="inlineStr"/>
+      <c r="K1322" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
     </row>
     <row r="1323">
       <c r="A1323" t="n">
@@ -58745,7 +58993,11 @@
         <v>1</v>
       </c>
       <c r="J1389" t="inlineStr"/>
-      <c r="K1389" t="inlineStr"/>
+      <c r="K1389" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
     </row>
     <row r="1390">
       <c r="A1390" t="n">
@@ -58786,7 +59038,11 @@
       <c r="J1390" t="n">
         <v>2</v>
       </c>
-      <c r="K1390" t="inlineStr"/>
+      <c r="K1390" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
     </row>
     <row r="1391">
       <c r="A1391" t="n">
@@ -59169,7 +59425,11 @@
         <v>1</v>
       </c>
       <c r="J1399" t="inlineStr"/>
-      <c r="K1399" t="inlineStr"/>
+      <c r="K1399" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
     </row>
     <row r="1400">
       <c r="A1400" t="n">
@@ -61413,7 +61673,11 @@
         <v>1</v>
       </c>
       <c r="J1451" t="inlineStr"/>
-      <c r="K1451" t="inlineStr"/>
+      <c r="K1451" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
     </row>
     <row r="1452">
       <c r="A1452" t="n">
@@ -61571,7 +61835,11 @@
         <v>1</v>
       </c>
       <c r="J1455" t="inlineStr"/>
-      <c r="K1455" t="inlineStr"/>
+      <c r="K1455" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
     </row>
     <row r="1456">
       <c r="A1456" t="n">
@@ -64108,7 +64376,11 @@
       <c r="H1516" t="inlineStr"/>
       <c r="I1516" t="inlineStr"/>
       <c r="J1516" t="inlineStr"/>
-      <c r="K1516" t="inlineStr"/>
+      <c r="K1516" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
     </row>
     <row r="1517">
       <c r="A1517" t="n">
@@ -64324,7 +64596,11 @@
       <c r="J1522" t="n">
         <v>1</v>
       </c>
-      <c r="K1522" t="inlineStr"/>
+      <c r="K1522" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
     </row>
     <row r="1523">
       <c r="A1523" t="n">
@@ -65063,7 +65339,11 @@
       <c r="H1541" t="inlineStr"/>
       <c r="I1541" t="inlineStr"/>
       <c r="J1541" t="inlineStr"/>
-      <c r="K1541" t="inlineStr"/>
+      <c r="K1541" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
     </row>
     <row r="1542">
       <c r="A1542" t="n">
@@ -70207,7 +70487,11 @@
       <c r="J1661" t="n">
         <v>2</v>
       </c>
-      <c r="K1661" t="inlineStr"/>
+      <c r="K1661" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
     </row>
     <row r="1662">
       <c r="A1662" t="n">
@@ -70795,7 +71079,11 @@
         <v>1</v>
       </c>
       <c r="J1675" t="inlineStr"/>
-      <c r="K1675" t="inlineStr"/>
+      <c r="K1675" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
     </row>
     <row r="1676">
       <c r="A1676" t="n">
@@ -73305,7 +73593,11 @@
       <c r="J1733" t="n">
         <v>2</v>
       </c>
-      <c r="K1733" t="inlineStr"/>
+      <c r="K1733" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
     </row>
     <row r="1734">
       <c r="A1734" t="n">
@@ -74522,7 +74814,11 @@
       <c r="H1762" t="inlineStr"/>
       <c r="I1762" t="inlineStr"/>
       <c r="J1762" t="inlineStr"/>
-      <c r="K1762" t="inlineStr"/>
+      <c r="K1762" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
     </row>
     <row r="1763">
       <c r="A1763" t="n">
@@ -75605,7 +75901,11 @@
       <c r="H1791" t="inlineStr"/>
       <c r="I1791" t="inlineStr"/>
       <c r="J1791" t="inlineStr"/>
-      <c r="K1791" t="inlineStr"/>
+      <c r="K1791" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
     </row>
     <row r="1792">
       <c r="A1792" t="n">
